--- a/docs/reports/內在價值報告_20260907.xlsx
+++ b/docs/reports/內在價值報告_20260907.xlsx
@@ -15,11 +15,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="方法與免責" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'投資總覽'!$A$1:$AF$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'估值模型明細'!$A$1:$Q$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五檔價位帶'!$A$1:$L$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'關鍵財務指標'!$A$1:$AC$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'AI投資建議'!$A$1:$M$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'投資總覽'!$A$1:$AF$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'估值模型明細'!$A$1:$Q$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'五檔價位帶'!$A$1:$L$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'關鍵財務指標'!$A$1:$AC$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'AI投資建議'!$A$1:$M$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -56,7 +56,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8CBAD"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -138,6 +143,21 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -521,7 +541,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF3"/>
+  <dimension ref="A1:AF4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
@@ -960,9 +980,131 @@
       </c>
       <c r="AF3" s="8" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="B4" s="12" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>谷歌-A</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr"/>
+      <c r="E4" s="12" t="inlineStr">
+        <is>
+          <t>mature</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr"/>
+      <c r="H4" s="14" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>62.856</v>
+      </c>
+      <c r="J4" s="14" t="n">
+        <v>2.0172</v>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>15.3128</v>
+      </c>
+      <c r="L4" s="15" t="n">
+        <v>438.5</v>
+      </c>
+      <c r="M4" s="15" t="n">
+        <v>25</v>
+      </c>
+      <c r="N4" s="14" t="n">
+        <v>47.142</v>
+      </c>
+      <c r="O4" s="12" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="P4" s="16" t="inlineStr">
+        <is>
+          <t>非常昂貴</t>
+        </is>
+      </c>
+      <c r="Q4" s="12" t="inlineStr">
+        <is>
+          <t>非常昂貴</t>
+        </is>
+      </c>
+      <c r="R4" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="S4" s="12" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="T4" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="V4" s="12" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W4" s="12" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="X4" s="13" t="inlineStr">
+        <is>
+          <t>高淨利率但ROIC僅5%，淨負債且EPS五年複合成長率-33.87%，獲利品質存疑</t>
+        </is>
+      </c>
+      <c r="Y4" s="15" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="Z4" s="15" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA4" s="15" t="n">
+        <v>61.6</v>
+      </c>
+      <c r="AB4" s="15" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="AC4" s="12" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AD4" s="12" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="AE4" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AF4" s="13" t="inlineStr">
+        <is>
+          <t>行情總股本(12,230,000,000)與財報EPS反推(145,707,017,544)差異&gt;25%，已改用反推值 / 缺關鍵科目：cfo,capex,d_and_a</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AF3"/>
-  <conditionalFormatting sqref="R2:R3">
+  <autoFilter ref="A1:AF4"/>
+  <conditionalFormatting sqref="R2:R4">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -971,7 +1113,7 @@
       </dataBar>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L3">
+  <conditionalFormatting sqref="L2:L4">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="num" val="-60"/>
@@ -993,7 +1135,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
@@ -1103,127 +1245,184 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>00700</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>腾讯控股</t>
         </is>
       </c>
-      <c r="C2" s="14" t="n">
+      <c r="C2" s="19" t="n">
         <v>442.8</v>
       </c>
-      <c r="D2" s="14" t="n">
+      <c r="D2" s="19" t="n">
         <v>659.7439000000001</v>
       </c>
-      <c r="E2" s="14" t="n">
+      <c r="E2" s="19" t="n">
         <v>282.2421</v>
       </c>
-      <c r="F2" s="14" t="n">
+      <c r="F2" s="19" t="n">
         <v>469.194</v>
       </c>
-      <c r="G2" s="14" t="inlineStr"/>
-      <c r="H2" s="14" t="n">
+      <c r="G2" s="19" t="inlineStr"/>
+      <c r="H2" s="19" t="n">
         <v>684.9804</v>
       </c>
-      <c r="I2" s="14" t="n">
+      <c r="I2" s="19" t="n">
         <v>368.7076</v>
       </c>
-      <c r="J2" s="14" t="n">
+      <c r="J2" s="19" t="n">
         <v>459.2987</v>
       </c>
-      <c r="K2" s="14" t="n">
+      <c r="K2" s="19" t="n">
         <v>3850.9893</v>
       </c>
-      <c r="L2" s="14" t="n">
+      <c r="L2" s="19" t="n">
         <v>609.7476</v>
       </c>
-      <c r="M2" s="14" t="n">
+      <c r="M2" s="19" t="n">
         <v>9.17</v>
       </c>
-      <c r="N2" s="14" t="n">
+      <c r="N2" s="19" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="O2" s="12" t="n">
+      <c r="O2" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="P2" s="13" t="inlineStr">
+      <c r="P2" s="18" t="inlineStr">
         <is>
           <t>{"graham_number": 0.102, "graham_formula": 0.102, "buffett_oe": 0.245, "epv": 0.204, "damodaran_fcff": 0.245, "ri_pb": 0.051, "ddm": 0.051}</t>
         </is>
       </c>
-      <c r="Q2" s="13" t="inlineStr">
+      <c r="Q2" s="18" t="inlineStr">
         <is>
           <t>{"graham_number": {"EPS(3年均)": 20.938, "BVPS": 124.7758}, "graham_formula": {"g(上限10%)": 0.08, "Y公司債": 0.056}, "ncav": {"NCAV/股": 0.0, "NNWC/股": -47.8878, "net-net買點": 0.0}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 202308000000.0, "g1": 0.1058, "永續g": 0.03, "門檻報酬r": 0.0905, "非營運投資(折70%)": 642665100000.0}, "epv": {"常態營業利益率": 0.3189, "常態NOPAT": 206641814252.0, "WACC": 0.0917, "淨現金": -12924000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.1076, "永續g": 0.03, "目標營業利益率": 0.3189, "WACC": 0.0917, "終值WACC": 0.0995, "有效稅率": 0.1678, "終值佔比": 0.565}, "ri_pb": {"常態ROE": 0.2271, "股權成本r": 0.0995, "留存成長g": 0.0945, "合理PB": 26.512}, "ddm": {"DPS": 4.8076, "g": 0.0895, "r": 0.0995}}</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>600519</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>贵州茅台</t>
         </is>
       </c>
-      <c r="C3" s="14" t="n">
+      <c r="C3" s="19" t="n">
         <v>1316.81</v>
       </c>
-      <c r="D3" s="14" t="n">
+      <c r="D3" s="19" t="n">
         <v>1186.8339</v>
       </c>
-      <c r="E3" s="14" t="n">
+      <c r="E3" s="19" t="n">
         <v>544.9149</v>
       </c>
-      <c r="F3" s="14" t="n">
+      <c r="F3" s="19" t="n">
         <v>2058.441</v>
       </c>
-      <c r="G3" s="14" t="n">
+      <c r="G3" s="19" t="n">
         <v>171.005</v>
       </c>
-      <c r="H3" s="14" t="n">
+      <c r="H3" s="19" t="n">
         <v>869.8927</v>
       </c>
-      <c r="I3" s="14" t="n">
+      <c r="I3" s="19" t="n">
         <v>838.7816</v>
       </c>
-      <c r="J3" s="14" t="n">
+      <c r="J3" s="19" t="n">
         <v>1283.6279</v>
       </c>
-      <c r="K3" s="14" t="n">
+      <c r="K3" s="19" t="n">
         <v>2189.9672</v>
       </c>
-      <c r="L3" s="14" t="n">
+      <c r="L3" s="19" t="n">
         <v>2579.5722</v>
       </c>
-      <c r="M3" s="14" t="n">
+      <c r="M3" s="19" t="n">
         <v>8.9</v>
       </c>
-      <c r="N3" s="14" t="n">
+      <c r="N3" s="19" t="n">
         <v>8.9</v>
       </c>
-      <c r="O3" s="12" t="n">
+      <c r="O3" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="P3" s="13" t="inlineStr">
+      <c r="P3" s="18" t="inlineStr">
         <is>
           <t>{"graham_number": 0.1, "graham_formula": 0.1, "ncav": 0.02, "buffett_oe": 0.24, "epv": 0.2, "damodaran_fcff": 0.24, "ri_pb": 0.05, "ddm": 0.05}</t>
         </is>
       </c>
-      <c r="Q3" s="13" t="inlineStr">
+      <c r="Q3" s="18" t="inlineStr">
         <is>
           <t>{"graham_number": {"EPS(3年均)": 65.66, "BVPS": 200.9898}, "graham_formula": {"g(上限10%)": 0.1, "Y公司債": 0.04}, "ncav": {"NCAV/股": 171.005, "NNWC/股": 29.7768, "net-net買點": 114.0604}, "buffett_oe": {"業主盈餘(TTM,中位3年)": 64728275253.0, "g1": 0.0333, "永續g": 0.021, "門檻報酬r": 0.085, "非營運投資(折70%)": 103039151.0}, "epv": {"常態營業利益率": 0.6873, "常態NOPAT": 88559729570.0, "WACC": 0.089, "淨現金": 53275114111.0}, "damodaran_fcff": {"銷售/資本": 0.875, "g1": 0.1049, "永續g": 0.021, "目標營業利益率": 0.6873, "WACC": 0.089, "終值WACC": 0.089, "有效稅率": 0.2562, "終值佔比": 0.538}, "ri_pb": {"常態ROE": 0.3272, "股權成本r": 0.089, "留存成長g": 0.0649, "合理PB": 10.896}, "ddm": {"DPS": 54.0882, "g": 0.0666, "r": 0.089}}</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>谷歌-A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="D4" s="19" t="n">
+        <v>62.856</v>
+      </c>
+      <c r="E4" s="19" t="n">
+        <v>14.6499</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>15.3128</v>
+      </c>
+      <c r="G4" s="19" t="n">
+        <v>0.4257</v>
+      </c>
+      <c r="H4" s="19" t="inlineStr"/>
+      <c r="I4" s="19" t="n">
+        <v>2.0172</v>
+      </c>
+      <c r="J4" s="19" t="n">
+        <v>3.797</v>
+      </c>
+      <c r="K4" s="19" t="n">
+        <v>806.1659</v>
+      </c>
+      <c r="L4" s="19" t="inlineStr"/>
+      <c r="M4" s="19" t="n">
+        <v>8.789999999999999</v>
+      </c>
+      <c r="N4" s="19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="O4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="P4" s="18" t="inlineStr">
+        <is>
+          <t>{"graham_number": 0.141, "graham_formula": 0.141, "ncav": 0.028, "epv": 0.282, "damodaran_fcff": 0.338, "ri_pb": 0.07}</t>
+        </is>
+      </c>
+      <c r="Q4" s="18" t="inlineStr">
+        <is>
+          <t>{"graham_number": {"EPS(3年均)": 2.17, "BVPS": 4.3957}, "graham_formula": {"g(上限10%)": -0.3387, "Y公司債": 0.053}, "ncav": {"NCAV/股": 0.4257, "NNWC/股": -1.1579, "net-net買點": 0.2839}, "epv": {"常態營業利益率": 0.2905, "常態NOPAT": 30294406765.0, "WACC": 0.0879, "淨現金": -50765000000.0}, "damodaran_fcff": {"銷售/資本": 0.8, "g1": 0.1439, "永續g": 0.04, "目標營業利益率": 0.2905, "WACC": 0.0879, "終值WACC": 0.088, "有效稅率": 0.24, "終值佔比": 0.706}, "ri_pb": {"常態ROE": 1.0, "股權成本r": 0.088, "留存成長g": 0.083, "合理PB": 183.4}}</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q3"/>
+  <autoFilter ref="A1:Q4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1234,7 +1433,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
@@ -1405,8 +1604,54 @@
         <v>890.1254</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>谷歌-A</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="E4" s="14" t="n">
+        <v>31.428</v>
+      </c>
+      <c r="F4" s="14" t="n">
+        <v>47.142</v>
+      </c>
+      <c r="G4" s="14" t="n">
+        <v>72.28449999999999</v>
+      </c>
+      <c r="H4" s="14" t="n">
+        <v>94.2841</v>
+      </c>
+      <c r="I4" s="14" t="n">
+        <v>94.2841</v>
+      </c>
+      <c r="J4" s="16" t="inlineStr">
+        <is>
+          <t>非常昂貴</t>
+        </is>
+      </c>
+      <c r="K4" s="14" t="n">
+        <v>5.3847</v>
+      </c>
+      <c r="L4" s="14" t="n">
+        <v>47.142</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L3"/>
+  <autoFilter ref="A1:L4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1417,7 +1662,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC3"/>
+  <dimension ref="A1:AC4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
@@ -1599,197 +1844,282 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="inlineStr">
+      <c r="A2" s="17" t="inlineStr">
         <is>
           <t>00700</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="18" t="inlineStr">
         <is>
           <t>腾讯控股</t>
         </is>
       </c>
-      <c r="C2" s="12" t="n">
+      <c r="C2" s="17" t="n">
         <v>778561000000</v>
       </c>
-      <c r="D2" s="12" t="n">
+      <c r="D2" s="17" t="n">
         <v>235508000000</v>
       </c>
-      <c r="E2" s="12" t="n">
+      <c r="E2" s="17" t="n">
         <v>305848000000</v>
       </c>
-      <c r="F2" s="12" t="n">
+      <c r="F2" s="17" t="n">
         <v>193325000000</v>
       </c>
-      <c r="G2" s="12" t="n">
+      <c r="G2" s="17" t="n">
         <v>202308000000</v>
       </c>
-      <c r="H2" s="12" t="n">
+      <c r="H2" s="17" t="n">
         <v>57.39</v>
       </c>
-      <c r="I2" s="12" t="n">
+      <c r="I2" s="17" t="n">
         <v>33.21</v>
       </c>
-      <c r="J2" s="12" t="n">
+      <c r="J2" s="17" t="n">
         <v>30.25</v>
       </c>
-      <c r="K2" s="12" t="n">
+      <c r="K2" s="17" t="n">
         <v>24.83</v>
       </c>
-      <c r="L2" s="12" t="n">
+      <c r="L2" s="17" t="n">
         <v>20.73</v>
       </c>
-      <c r="M2" s="12" t="n">
+      <c r="M2" s="17" t="n">
         <v>22.71</v>
       </c>
-      <c r="N2" s="12" t="n">
+      <c r="N2" s="17" t="n">
         <v>0.814677</v>
       </c>
-      <c r="O2" s="12" t="n">
+      <c r="O2" s="17" t="n">
         <v>18.73</v>
       </c>
-      <c r="P2" s="12" t="n">
+      <c r="P2" s="17" t="n">
         <v>43.39</v>
       </c>
-      <c r="Q2" s="12" t="n">
+      <c r="Q2" s="17" t="n">
         <v>0.415395</v>
       </c>
-      <c r="R2" s="12" t="n">
+      <c r="R2" s="17" t="n">
         <v>1.287</v>
       </c>
-      <c r="S2" s="12" t="n">
+      <c r="S2" s="17" t="n">
         <v>19.213957</v>
       </c>
-      <c r="T2" s="12" t="n">
+      <c r="T2" s="17" t="n">
         <v>-12924000000</v>
       </c>
-      <c r="U2" s="12" t="n">
+      <c r="U2" s="17" t="n">
         <v>918093000000</v>
       </c>
-      <c r="V2" s="12" t="n">
+      <c r="V2" s="17" t="n">
         <v>10.76</v>
       </c>
-      <c r="W2" s="12" t="n">
+      <c r="W2" s="17" t="n">
         <v>9.4</v>
       </c>
-      <c r="X2" s="12" t="n">
+      <c r="X2" s="17" t="n">
         <v>22.45</v>
       </c>
-      <c r="Y2" s="12" t="n">
+      <c r="Y2" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="Z2" s="12" t="n">
+      <c r="Z2" s="17" t="n">
         <v>18.58</v>
       </c>
-      <c r="AA2" s="12" t="n">
+      <c r="AA2" s="17" t="n">
         <v>9</v>
       </c>
-      <c r="AB2" s="12" t="n">
+      <c r="AB2" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="AC2" s="12" t="inlineStr">
+      <c r="AC2" s="17" t="inlineStr">
         <is>
           <t>4/7</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="17" t="inlineStr">
         <is>
           <t>600519</t>
         </is>
       </c>
-      <c r="B3" s="13" t="inlineStr">
+      <c r="B3" s="18" t="inlineStr">
         <is>
           <t>贵州茅台</t>
         </is>
       </c>
-      <c r="C3" s="12" t="n">
+      <c r="C3" s="17" t="n">
         <v>173238481420.15</v>
       </c>
-      <c r="D3" s="12" t="n">
+      <c r="D3" s="17" t="n">
         <v>84356973951.20999</v>
       </c>
-      <c r="E3" s="12" t="n">
+      <c r="E3" s="17" t="n">
         <v>119093894077.08</v>
       </c>
-      <c r="F3" s="12" t="n">
+      <c r="F3" s="17" t="n">
         <v>116730152217.62</v>
       </c>
-      <c r="G3" s="12" t="n">
+      <c r="G3" s="17" t="n">
         <v>64728275253.3</v>
       </c>
-      <c r="H3" s="12" t="n">
+      <c r="H3" s="17" t="n">
         <v>90.42</v>
       </c>
-      <c r="I3" s="12" t="n">
+      <c r="I3" s="17" t="n">
         <v>65.48999999999999</v>
       </c>
-      <c r="J3" s="12" t="n">
+      <c r="J3" s="17" t="n">
         <v>48.69</v>
       </c>
-      <c r="K3" s="12" t="n">
+      <c r="K3" s="17" t="n">
         <v>67.38</v>
       </c>
-      <c r="L3" s="12" t="n">
+      <c r="L3" s="17" t="n">
         <v>33.57</v>
       </c>
-      <c r="M3" s="12" t="n">
+      <c r="M3" s="17" t="n">
         <v>32.72</v>
       </c>
-      <c r="N3" s="12" t="n">
+      <c r="N3" s="17" t="n">
         <v>0.889428</v>
       </c>
-      <c r="O3" s="12" t="n">
+      <c r="O3" s="17" t="n">
         <v>42.62</v>
       </c>
-      <c r="P3" s="12" t="n">
+      <c r="P3" s="17" t="n">
         <v>15.19</v>
       </c>
-      <c r="Q3" s="12" t="n">
+      <c r="Q3" s="17" t="n">
         <v>0.0009700000000000001</v>
       </c>
-      <c r="R3" s="12" t="n">
+      <c r="R3" s="17" t="n">
         <v>5.589543</v>
       </c>
-      <c r="S3" s="12" t="n">
+      <c r="S3" s="17" t="n">
         <v>2498.931082</v>
       </c>
-      <c r="T3" s="12" t="n">
+      <c r="T3" s="17" t="n">
         <v>53275114111.02</v>
       </c>
-      <c r="U3" s="12" t="n">
+      <c r="U3" s="17" t="n">
         <v>147198786.54</v>
       </c>
-      <c r="V3" s="12" t="n">
+      <c r="V3" s="17" t="n">
         <v>10.49</v>
       </c>
-      <c r="W3" s="12" t="n">
+      <c r="W3" s="17" t="n">
         <v>11.92</v>
       </c>
-      <c r="X3" s="12" t="n">
+      <c r="X3" s="17" t="n">
         <v>17.8</v>
       </c>
-      <c r="Y3" s="12" t="n">
+      <c r="Y3" s="17" t="n">
         <v>12.05</v>
       </c>
-      <c r="Z3" s="12" t="n">
+      <c r="Z3" s="17" t="n">
         <v>80.15000000000001</v>
       </c>
-      <c r="AA3" s="12" t="n">
+      <c r="AA3" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="AB3" s="12" t="n">
+      <c r="AB3" s="17" t="n">
         <v>10</v>
       </c>
-      <c r="AC3" s="12" t="inlineStr">
+      <c r="AC3" s="17" t="inlineStr">
         <is>
           <t>5/7</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>谷歌-A</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="n">
+        <v>137196000000</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>118452000000</v>
+      </c>
+      <c r="E4" s="17" t="inlineStr"/>
+      <c r="F4" s="17" t="inlineStr"/>
+      <c r="G4" s="17" t="inlineStr"/>
+      <c r="H4" s="17" t="n">
+        <v>61.61</v>
+      </c>
+      <c r="I4" s="17" t="n">
+        <v>33.12</v>
+      </c>
+      <c r="J4" s="17" t="n">
+        <v>86.34</v>
+      </c>
+      <c r="K4" s="17" t="inlineStr"/>
+      <c r="L4" s="17" t="n">
+        <v>18.49</v>
+      </c>
+      <c r="M4" s="17" t="n">
+        <v>100</v>
+      </c>
+      <c r="N4" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O4" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="P4" s="17" t="n">
+        <v>30.53</v>
+      </c>
+      <c r="Q4" s="17" t="n">
+        <v>0.166556</v>
+      </c>
+      <c r="R4" s="17" t="n">
+        <v>2.723981</v>
+      </c>
+      <c r="S4" s="17" t="n">
+        <v>99</v>
+      </c>
+      <c r="T4" s="17" t="n">
+        <v>-50765000000</v>
+      </c>
+      <c r="U4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" s="17" t="n">
+        <v>14.39</v>
+      </c>
+      <c r="W4" s="17" t="n">
+        <v>14.88</v>
+      </c>
+      <c r="X4" s="17" t="n">
+        <v>18.23</v>
+      </c>
+      <c r="Y4" s="17" t="n">
+        <v>-33.87</v>
+      </c>
+      <c r="Z4" s="17" t="inlineStr"/>
+      <c r="AA4" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" s="17" t="inlineStr">
+        <is>
+          <t>3/7</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AC3"/>
+  <autoFilter ref="A1:AC4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1800,7 +2130,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9.4" customWidth="1" min="1" max="1"/>
@@ -2003,9 +2333,68 @@
       </c>
       <c r="M3" s="8" t="inlineStr"/>
     </row>
+    <row r="4" ht="118" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>GOOGL</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>谷歌-A</t>
+        </is>
+      </c>
+      <c r="C4" s="12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D4" s="12" t="inlineStr">
+        <is>
+          <t>★★☆☆☆</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="inlineStr">
+        <is>
+          <t>非常昂貴</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
+        <is>
+          <t>非常昂貴</t>
+        </is>
+      </c>
+      <c r="G4" s="12" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>高淨利率但ROIC僅5%，淨負債且EPS五年複合成長率-33.87%，獲利品質存疑</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>獲利品質：淨利率86.34%異常高，但EPS_CAGR_5年-33.87%且ROIC僅5.0%，成長不可持續；關鍵現金流數據缺失（cfo/capex/d_and_a），無法驗證業主盈餘。資產負債穩健（負債權益比0.166556，利息保障倍數99.0），但淨現金-50765百萬表淨負債風險。成長依賴營收CAGR_10年18.23%，然ROIC遠低於ROE(10年中位)100.0%，資本配置效率低。估值：加權內在價值62.856，現價338.46，價格/內在價值5.3847，安全邊際MOS 0.25未達標。結論：財務體質矛盾，價格嚴重高估，建議觀察ROIC改善及現金流補齊。</t>
+        </is>
+      </c>
+      <c r="J4" s="13" t="inlineStr">
+        <is>
+          <t>淨利率86.34%不可持續 / EPS五年複合成長率-33.87% / ROIC與ROE嚴重背離</t>
+        </is>
+      </c>
+      <c r="K4" s="12" t="inlineStr">
+        <is>
+          <t>qwen-plus</t>
+        </is>
+      </c>
+      <c r="L4" s="12" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="M4" s="13" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:M3"/>
-  <conditionalFormatting sqref="C2:C3">
+  <autoFilter ref="A1:M4"/>
+  <conditionalFormatting sqref="C2:C4">
     <cfRule type="dataBar" priority="1">
       <dataBar>
         <cfvo type="num" val="0"/>
@@ -2032,12 +2421,12 @@
   </cols>
   <sheetData>
     <row r="1" ht="78" customHeight="1">
-      <c r="A1" s="15" t="inlineStr">
+      <c r="A1" s="20" t="inlineStr">
         <is>
           <t>章節</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="21" t="inlineStr">
         <is>
           <t>內容</t>
         </is>
@@ -2049,7 +2438,7 @@
           <t>① 資料來源</t>
         </is>
       </c>
-      <c r="B2" s="17" t="inlineStr">
+      <c r="B2" s="22" t="inlineStr">
         <is>
           <t>東方財富 F10 標準化財報（港股→港交所披露易；A股→滬深北定期報告；美股→SEC 10-K/10-Q）；行情 push2 即時報價；匯率 open.er-api / frankfurter。全部原始回應留存於 data/raw。</t>
         </is>
@@ -2061,7 +2450,7 @@
           <t>② 內在價值 8 模型</t>
         </is>
       </c>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t>①葛拉漢數字√(22.5×EPS₃ᵃᵛᵍ×BVPS) ②葛拉漢修正公式EPS×(8.5+2g)×4.4/Y ③NCAV清算價值(下限) ④巴菲特業主盈餘10年兩段DCF(門檻報酬=無風險利率+5.5%) ⑤EPV常態NOPAT/WACC+淨現金 ⑥達摩達蘭FCFF兩段DCF(銷售/資本再投資+合成評級WACC+ROIC推導終值再投資率) ⑦剩餘收益合理PB=(ROE−g)/(r−g) ⑧股利折現。</t>
         </is>
@@ -2073,7 +2462,7 @@
           <t>③ 加權方式</t>
         </is>
       </c>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="22" t="inlineStr">
         <is>
           <t>依公司畫像（financial / growth / mature / loss_making）給各模型權重後加權；同時取所有模型的 P25~P75 作為價值區間，避免單一模型誤導。</t>
         </is>
@@ -2085,7 +2474,7 @@
           <t>④ 估值區間定義</t>
         </is>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t>價格/內在價值 ≤0.50 非常便宜；≤0.75 便宜；≤1.15 合理；≤1.50 昂貴；&gt;1.50 非常昂貴。區間切換設 2% 遲滯緩衝，避免邊界抖動誤報。</t>
         </is>
@@ -2097,7 +2486,7 @@
           <t>⑤ 信心分數</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="22" t="inlineStr">
         <is>
           <t>由資料完整度、歷史年數、模型分歧度、獲利連續性、可用模型數 5 項加權；低於 50 建議只當篩選線索，不作決策依據。此分數由系統自動計算，不必手填。</t>
         </is>
@@ -2109,7 +2498,7 @@
           <t>⑥ 安全邊際 MOS</t>
         </is>
       </c>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>全域預設 25%（settings.yaml valuation.margin_of_safety）；watchlist 的 mos= 可覆寫個股。安全買點 = 內在價值 × (1−MOS)。此欄是格雷厄姆買入紀律，不會改五檔區間切點。</t>
         </is>
@@ -2121,7 +2510,7 @@
           <t>⑦ 幣別處理</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>財報幣別≠交易幣別者（如騰訊人民幣報表/港幣交易）已換算；並以財報 EPS 反推股數交叉驗證行情總股本，偏離 &gt;25% 自動改用反推值並列於「警示」。</t>
         </is>
@@ -2133,7 +2522,7 @@
           <t>⑧ AI 反幻覺</t>
         </is>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>AI 僅獲得本檔內數字與精簡 Excel 附件，Prompt 禁止外部事實；輸出經 JSON Schema 驗證與可疑敘述掃描，結果記於「品質旗標」欄。旗標非空者請人工複核。</t>
         </is>
@@ -2145,7 +2534,7 @@
           <t>⑨ 已知限制</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>①合成評級/β/ERP 為近似值，標 [年度校準] 者需每年 1 月手動更新 ②金融股 FCFF 不適用，已改以剩餘收益與 DDM 為主 ③一次性損益與會計政策變更未逐項調整 ④終值佔比高的個股對假設極敏感（見估值明細）。</t>
         </is>
@@ -2157,7 +2546,7 @@
           <t>⑩ 免責聲明</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>本檔為程式化研究輔助，非投資建議。所有估值皆為假設下的條件性結論，請自行覆核假設與原始財報後獨立決策；投資有風險。</t>
         </is>
